--- a/data/trans_orig/P19C11_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P19C11_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por implantes / solo 2023 en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por implantes / solo 2023 en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6252</t>
+          <t>6365</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>10849</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>322</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13614</t>
+          <t>13397</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>377195</t>
+          <t>377082</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>291081</t>
+          <t>292692</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>673374</t>
+          <t>673591</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>686820</t>
+          <t>686666</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,98%</t>
+          <t>99,95%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21329</t>
+          <t>20634</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>2694</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16419</t>
+          <t>16876</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10582</t>
+          <t>10729</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31517</t>
+          <t>31732</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>381022</t>
+          <t>381717</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>397521</t>
+          <t>397522</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>483273</t>
+          <t>482816</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>496676</t>
+          <t>496998</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>870525</t>
+          <t>870310</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>891460</t>
+          <t>891313</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10942</t>
+          <t>10908</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28364</t>
+          <t>28542</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>6718</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16405</t>
+          <t>16822</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20174</t>
+          <t>19915</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42269</t>
+          <t>40556</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>495678</t>
+          <t>495500</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>513100</t>
+          <t>513134</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>515476</t>
+          <t>515059</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>525227</t>
+          <t>525163</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1013654</t>
+          <t>1015367</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1035749</t>
+          <t>1036008</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13941</t>
+          <t>11776</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52899</t>
+          <t>50187</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29778</t>
+          <t>30101</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47788</t>
+          <t>49926</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40602</t>
+          <t>43094</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90699</t>
+          <t>94100</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>810029</t>
+          <t>812741</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>848987</t>
+          <t>851152</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>652804</t>
+          <t>650666</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>670814</t>
+          <t>670491</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1472820</t>
+          <t>1469419</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1522917</t>
+          <t>1520425</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21921</t>
+          <t>21212</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42243</t>
+          <t>41825</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29361</t>
+          <t>29752</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47047</t>
+          <t>46174</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>55758</t>
+          <t>55296</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81324</t>
+          <t>81216</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>504336</t>
+          <t>504754</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>524658</t>
+          <t>525367</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>487479</t>
+          <t>488352</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>505165</t>
+          <t>504774</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>999781</t>
+          <t>999889</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1025347</t>
+          <t>1025809</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,89%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22933</t>
+          <t>23570</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40686</t>
+          <t>40438</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7394</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37058</t>
+          <t>36538</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27496</t>
+          <t>26135</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>72511</t>
+          <t>73082</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>318667</t>
+          <t>318915</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>336420</t>
+          <t>335783</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>562851</t>
+          <t>563371</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>592515</t>
+          <t>592414</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>886751</t>
+          <t>886180</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>931766</t>
+          <t>933127</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11232</t>
+          <t>11668</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23774</t>
+          <t>24608</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14081</t>
+          <t>14194</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26233</t>
+          <t>26864</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28411</t>
+          <t>28783</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46096</t>
+          <t>45988</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>251747</t>
+          <t>250913</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>264289</t>
+          <t>263853</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>382454</t>
+          <t>381823</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>394606</t>
+          <t>394493</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>638112</t>
+          <t>638220</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>655797</t>
+          <t>655425</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,79%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>111338</t>
+          <t>105752</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>168678</t>
+          <t>163532</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>113688</t>
+          <t>112396</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>160699</t>
+          <t>161142</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>236545</t>
+          <t>239540</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>314939</t>
+          <t>314375</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3185543</t>
+          <t>3190689</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3242883</t>
+          <t>3248469</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3418128</t>
+          <t>3417685</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3465139</t>
+          <t>3466431</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6618109</t>
+          <t>6618673</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6696503</t>
+          <t>6693508</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C11_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P19C11_2023-Edad-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>5616</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2661</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10849</t>
+          <t>13492</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13397</t>
+          <t>17567</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -838,17 +838,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>382220</t>
+          <t>377656</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>377082</t>
+          <t>373238</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>383447</t>
+          <t>378854</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>300880</t>
+          <t>339261</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>292692</t>
+          <t>329748</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>683099</t>
+          <t>716917</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>673591</t>
+          <t>704527</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>686666</t>
+          <t>720873</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>383447</t>
+          <t>378854</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>383447</t>
+          <t>378854</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>383447</t>
+          <t>378854</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>686988</t>
+          <t>722094</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>686988</t>
+          <t>722094</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>686988</t>
+          <t>722094</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10614</t>
+          <t>14834</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20634</t>
+          <t>27854</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,27 +1103,27 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8175</t>
+          <t>8065</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16876</t>
+          <t>16323</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>18789</t>
+          <t>22899</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10729</t>
+          <t>13617</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31732</t>
+          <t>37887</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>391737</t>
+          <t>431059</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>381717</t>
+          <t>418039</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>397522</t>
+          <t>438601</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,22 +1216,22 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>491517</t>
+          <t>474544</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>482816</t>
+          <t>466286</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>496998</t>
+          <t>479369</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>883253</t>
+          <t>905603</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>870310</t>
+          <t>890615</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>891313</t>
+          <t>914885</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>402351</t>
+          <t>445893</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>402351</t>
+          <t>445893</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>402351</t>
+          <t>445893</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>499692</t>
+          <t>482609</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>499692</t>
+          <t>482609</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>499692</t>
+          <t>482609</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>902042</t>
+          <t>928502</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>902042</t>
+          <t>928502</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>902042</t>
+          <t>928502</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>19783</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>11897</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28542</t>
+          <t>30623</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>13209</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6718</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16822</t>
+          <t>20315</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>29021</t>
+          <t>32992</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19915</t>
+          <t>23032</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40556</t>
+          <t>46128</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>505929</t>
+          <t>581341</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>495500</t>
+          <t>570501</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>513134</t>
+          <t>589227</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>520973</t>
+          <t>594073</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>515059</t>
+          <t>586967</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>525163</t>
+          <t>599089</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1026902</t>
+          <t>1175413</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1015367</t>
+          <t>1162277</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1036008</t>
+          <t>1185373</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>524042</t>
+          <t>601124</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>524042</t>
+          <t>601124</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>524042</t>
+          <t>601124</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>531881</t>
+          <t>607282</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>531881</t>
+          <t>607282</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>531881</t>
+          <t>607282</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1055923</t>
+          <t>1208405</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1055923</t>
+          <t>1208405</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1055923</t>
+          <t>1208405</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32181</t>
+          <t>34115</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11776</t>
+          <t>23476</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50187</t>
+          <t>46015</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38348</t>
+          <t>41919</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30101</t>
+          <t>33042</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49926</t>
+          <t>52230</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>70529</t>
+          <t>76034</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43094</t>
+          <t>62058</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94100</t>
+          <t>92304</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>830747</t>
+          <t>644184</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>812741</t>
+          <t>632284</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>851152</t>
+          <t>654823</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>662244</t>
+          <t>679838</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>650666</t>
+          <t>669527</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>670491</t>
+          <t>688715</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1492990</t>
+          <t>1324022</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1469419</t>
+          <t>1307752</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1520425</t>
+          <t>1337998</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>862928</t>
+          <t>678299</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>862928</t>
+          <t>678299</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>862928</t>
+          <t>678299</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>700592</t>
+          <t>721757</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>700592</t>
+          <t>721757</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>700592</t>
+          <t>721757</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1563519</t>
+          <t>1400056</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1563519</t>
+          <t>1400056</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1563519</t>
+          <t>1400056</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>30277</t>
+          <t>32392</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21212</t>
+          <t>23354</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41825</t>
+          <t>43778</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>36767</t>
+          <t>40163</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29752</t>
+          <t>32184</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46174</t>
+          <t>50136</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>67045</t>
+          <t>72555</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>55296</t>
+          <t>59058</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81216</t>
+          <t>86797</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>516302</t>
+          <t>560963</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>504754</t>
+          <t>549577</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>525367</t>
+          <t>570001</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>497759</t>
+          <t>555686</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>488352</t>
+          <t>545713</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>504774</t>
+          <t>563665</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1014060</t>
+          <t>1116649</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>999889</t>
+          <t>1102407</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1025809</t>
+          <t>1130146</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,03%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>546579</t>
+          <t>593355</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>546579</t>
+          <t>593355</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>546579</t>
+          <t>593355</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>534526</t>
+          <t>595849</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>534526</t>
+          <t>595849</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>534526</t>
+          <t>595849</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1081105</t>
+          <t>1189204</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1081105</t>
+          <t>1189204</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1081105</t>
+          <t>1189204</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>31053</t>
+          <t>33635</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23570</t>
+          <t>25339</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40438</t>
+          <t>44473</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>24409</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>18266</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36538</t>
+          <t>32130</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>53444</t>
+          <t>58044</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26135</t>
+          <t>46927</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>73082</t>
+          <t>70658</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>328300</t>
+          <t>364109</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>318915</t>
+          <t>353271</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>335783</t>
+          <t>372405</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>577518</t>
+          <t>404516</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>563371</t>
+          <t>396795</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>592414</t>
+          <t>410659</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>905818</t>
+          <t>768625</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>886180</t>
+          <t>756011</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>933127</t>
+          <t>779742</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>359353</t>
+          <t>397744</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>359353</t>
+          <t>397744</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>359353</t>
+          <t>397744</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>599909</t>
+          <t>428925</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>599909</t>
+          <t>428925</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>599909</t>
+          <t>428925</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>959262</t>
+          <t>826669</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>959262</t>
+          <t>826669</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>959262</t>
+          <t>826669</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>17209</t>
+          <t>19305</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11668</t>
+          <t>12116</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24608</t>
+          <t>27193</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>19662</t>
+          <t>20399</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14194</t>
+          <t>14082</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26864</t>
+          <t>27507</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,22 +2853,22 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>36871</t>
+          <t>39704</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28783</t>
+          <t>31532</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45988</t>
+          <t>51120</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>258312</t>
+          <t>283104</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>250913</t>
+          <t>275216</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>263853</t>
+          <t>290293</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>389025</t>
+          <t>425387</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>381823</t>
+          <t>418279</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>394493</t>
+          <t>431704</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,27 +2966,27 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>647337</t>
+          <t>708492</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>638220</t>
+          <t>697076</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>655425</t>
+          <t>716664</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>275521</t>
+          <t>302409</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>275521</t>
+          <t>302409</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>275521</t>
+          <t>302409</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>408687</t>
+          <t>445786</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>408687</t>
+          <t>445786</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>408687</t>
+          <t>445786</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>684208</t>
+          <t>748196</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>684208</t>
+          <t>748196</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>684208</t>
+          <t>748196</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>140674</t>
+          <t>155262</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>105752</t>
+          <t>133792</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>163532</t>
+          <t>180390</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>138912</t>
+          <t>152143</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>112396</t>
+          <t>134476</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>161142</t>
+          <t>173205</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>279587</t>
+          <t>307405</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>239540</t>
+          <t>279706</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>314375</t>
+          <t>341573</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3213547</t>
+          <t>3242416</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3190689</t>
+          <t>3217288</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3248469</t>
+          <t>3263886</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3439915</t>
+          <t>3473305</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3417685</t>
+          <t>3452243</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3466431</t>
+          <t>3490972</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6653461</t>
+          <t>6715720</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6618673</t>
+          <t>6681552</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6693508</t>
+          <t>6743419</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
